--- a/data/trans_camb/IP16B08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Provincia-trans_camb.xlsx
@@ -583,7 +583,7 @@
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>Almeria</t>
+          <t>Almería</t>
         </is>
       </c>
       <c r="B4" s="3" t="inlineStr">
@@ -739,7 +739,7 @@
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>Cadiz</t>
+          <t>Cádiz</t>
         </is>
       </c>
       <c r="B8" s="3" t="inlineStr">
@@ -895,7 +895,7 @@
     <row r="12">
       <c r="A12" s="1" t="inlineStr">
         <is>
-          <t>Cordoba</t>
+          <t>Córdoba</t>
         </is>
       </c>
       <c r="B12" s="3" t="inlineStr">
@@ -1363,7 +1363,7 @@
     <row r="24">
       <c r="A24" s="1" t="inlineStr">
         <is>
-          <t>Jaen</t>
+          <t>Jaén</t>
         </is>
       </c>
       <c r="B24" s="3" t="inlineStr">
@@ -1519,7 +1519,7 @@
     <row r="28">
       <c r="A28" s="1" t="inlineStr">
         <is>
-          <t>Malaga</t>
+          <t>Málaga</t>
         </is>
       </c>
       <c r="B28" s="3" t="inlineStr">
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 0,0</t>
+          <t>-71,21; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-31,66; 31,47</t>
+          <t>-29,88; 35,8</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 52,68</t>
+          <t>0,0; 51,16</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-71,29; 0,0</t>
+          <t>-71,21; 0,0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-38,2; 54,01</t>
+          <t>-32,77; 55,77</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 111,34</t>
+          <t>0,0; 104,97</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,68</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,69</t>
+          <t>0,0; 20,74</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-18,88; 6,91</t>
+          <t>-20,88; 6,95</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,4</t>
+          <t>0,0; 17,28</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-5,61; 8,72</t>
+          <t>-6,86; 9,44</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,51; 13,05</t>
+          <t>1,51; 12,32</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,08</t>
+          <t>0,0; 26,4</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,09</t>
+          <t>0,0; 26,17</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-20,34; 7,42</t>
+          <t>-21,3; 7,45</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 19,61</t>
+          <t>0,0; 20,89</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-5,68; 9,68</t>
+          <t>-6,97; 10,49</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,54; 15,0</t>
+          <t>1,53; 14,04</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/IP16B08-Provincia-trans_camb.xlsx
+++ b/data/trans_camb/IP16B08-Provincia-trans_camb.xlsx
@@ -1733,7 +1733,7 @@
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-71,21; 0,0</t>
+          <t>-69,66; 0,0</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>-29,88; 35,8</t>
+          <t>-30,83; 34,1</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,16</t>
+          <t>0,0; 53,35</t>
         </is>
       </c>
     </row>
@@ -1809,7 +1809,7 @@
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-71,21; 0,0</t>
+          <t>-69,66; 0,0</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
@@ -1819,12 +1819,12 @@
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>-32,77; 55,77</t>
+          <t>-36,72; 54,55</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>0,0; 104,97</t>
+          <t>0,0; 114,37</t>
         </is>
       </c>
     </row>
@@ -1879,32 +1879,32 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,28</t>
         </is>
       </c>
       <c r="D37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,74</t>
+          <t>0,0; 20,62</t>
         </is>
       </c>
       <c r="E37" s="2" t="inlineStr">
         <is>
-          <t>-20,88; 6,95</t>
+          <t>-19,6; 6,91</t>
         </is>
       </c>
       <c r="F37" s="2" t="inlineStr">
         <is>
-          <t>0,0; 17,28</t>
+          <t>0,0; 17,22</t>
         </is>
       </c>
       <c r="G37" s="2" t="inlineStr">
         <is>
-          <t>-6,86; 9,44</t>
+          <t>-6,8; 9,22</t>
         </is>
       </c>
       <c r="H37" s="2" t="inlineStr">
         <is>
-          <t>1,51; 12,32</t>
+          <t>1,48; 12,48</t>
         </is>
       </c>
     </row>
@@ -1955,32 +1955,32 @@
       </c>
       <c r="C39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,4</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="D39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,17</t>
+          <t>0,0; 25,98</t>
         </is>
       </c>
       <c r="E39" s="2" t="inlineStr">
         <is>
-          <t>-21,3; 7,45</t>
+          <t>-20,91; 7,4</t>
         </is>
       </c>
       <c r="F39" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,89</t>
+          <t>0,0; 20,81</t>
         </is>
       </c>
       <c r="G39" s="2" t="inlineStr">
         <is>
-          <t>-6,97; 10,49</t>
+          <t>-6,94; 10,21</t>
         </is>
       </c>
       <c r="H39" s="2" t="inlineStr">
         <is>
-          <t>1,53; 14,04</t>
+          <t>1,5; 14,25</t>
         </is>
       </c>
     </row>
